--- a/Dependencies/Ping_2018/acg/PTM_heatmap_data.xlsx
+++ b/Dependencies/Ping_2018/acg/PTM_heatmap_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,199 +458,199 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07859023409172909</v>
+        <v>0.05188555146100556</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1088903252845235</v>
+        <v>0.07166212401677137</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08069308884309082</v>
+        <v>0.05563127590331284</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05674346421686217</v>
+        <v>0.04257198272876307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06634191968555245</v>
+        <v>0.04494765250969844</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Missing TMT10_Lys_mono</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1452728569574386</v>
+        <v>0.006104182524824184</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1601700714940955</v>
+        <v>0.006073061357353506</v>
       </c>
       <c r="D3" t="n">
-        <v>0.148428163419408</v>
+        <v>0.01088438006803947</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1078125820120381</v>
+        <v>0.005772472234408552</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08801799245409929</v>
+        <v>0.00594895400863656</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Persulfide</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7126705318772706</v>
+        <v>0.007935437282271439</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9616535122511111</v>
+        <v>0.007894979764559556</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2744743021962067</v>
+        <v>0.008465628941808476</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2645664019111199</v>
+        <v>0.01010182641021497</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2318682935544556</v>
+        <v>0.0105759182375761</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1125269260858848</v>
+        <v>0.02807923961419125</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1367459898921922</v>
+        <v>0.02489955156514937</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1896582088136879</v>
+        <v>0.02721095017009867</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09575459586595492</v>
+        <v>0.02020365282042993</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06305766623577262</v>
+        <v>0.02908377515333429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Phosphorylation</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05001196714928215</v>
+        <v>0.0366250951489451</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05507824592879965</v>
+        <v>0.002429224542941402</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04417504863672855</v>
+        <v>0.003628126689346489</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03617395843824964</v>
+        <v>0.004329354175806414</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02693087828819456</v>
+        <v>0.003304974449242533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.940467897675515</v>
+        <v>0.01281878330213079</v>
       </c>
       <c r="C7" t="n">
-        <v>5.095687373343774</v>
+        <v>0.009109592036030258</v>
       </c>
       <c r="D7" t="n">
-        <v>5.080130593223783</v>
+        <v>0.01330313119427046</v>
       </c>
       <c r="E7" t="n">
-        <v>6.543230717506919</v>
+        <v>0.009380267380913897</v>
       </c>
       <c r="F7" t="n">
-        <v>5.139199798215468</v>
+        <v>0.002643979559394026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0107168501034176</v>
+        <v>0.01037711029220111</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01582708216344817</v>
+        <v>0.004858449085882804</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01178001296979428</v>
+        <v>0.01088438006803947</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006383639724396995</v>
+        <v>0.01731741670322566</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002627402759823859</v>
+        <v>0.003304974449242533</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5924036584944731</v>
+        <v>5.534051877005605</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9432940969415112</v>
+        <v>5.620618286230669</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7144577866180232</v>
+        <v>5.700391716744893</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4156458753885154</v>
+        <v>7.291353991087303</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3133177791089952</v>
+        <v>5.262180318083961</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06608724230440856</v>
+        <v>0.002441673009929674</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07280457795186161</v>
+        <v>0.01032420430750096</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03534003890938284</v>
+        <v>0.01330313119427046</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007092933027107771</v>
+        <v>0.00793714932231176</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01182331241920737</v>
+        <v>0.005287959118788052</v>
       </c>
     </row>
     <row r="11">
@@ -660,195 +660,195 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02560136413594205</v>
+        <v>0.0433396959262517</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03355341418651013</v>
+        <v>0.03826028655132709</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02473802723656799</v>
+        <v>0.02842032573321417</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02198809238403409</v>
+        <v>0.02597612505483849</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02364662483841473</v>
+        <v>0.02643979559394026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1250299178732054</v>
+        <v>0.7953749829845912</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1456091559037232</v>
+        <v>0.9552925515117066</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09424010375835425</v>
+        <v>0.2884360718030459</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03688325174096041</v>
+        <v>0.292952965896234</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02627402759823859</v>
+        <v>0.2313482114469773</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Acrylamide adduct</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07263642847871932</v>
+        <v>0.02807923961419125</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08040157739031673</v>
+        <v>0.02732877610809077</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07892608689762168</v>
+        <v>0.0362812668934649</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0773129699954747</v>
+        <v>0.01587429864462352</v>
       </c>
       <c r="F13" t="n">
-        <v>0.04729324967682947</v>
+        <v>0.03304974449242533</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.001786141683902934</v>
+        <v>0.0134292015546132</v>
       </c>
       <c r="C14" t="n">
-        <v>0.005697749578841343</v>
+        <v>0.01578995952911911</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00589000648489714</v>
+        <v>0.03446720354879165</v>
       </c>
       <c r="E14" t="n">
-        <v>0.006383639724396995</v>
+        <v>0.0115449444688171</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005254805519647718</v>
+        <v>0.01189790801727312</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Lys_mono</t>
+          <t>Acetylation</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.00595380561300978</v>
+        <v>0.006714600777306602</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01012933258460683</v>
+        <v>0.004251142950147454</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01178001296979428</v>
+        <v>0.003023438907788741</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007802226329818549</v>
+        <v>0.004329354175806414</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01050961103929544</v>
+        <v>0.00198298466954552</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Di-Methylation</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.001190761122601956</v>
+        <v>0.1660337646752178</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002532333146151708</v>
+        <v>0.1469680848479548</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000589000648489714</v>
+        <v>0.1027969228648172</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001418586605421554</v>
+        <v>0.03391327437715025</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0006568506899559648</v>
+        <v>0.02776178537363727</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Formylation</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01131223066471858</v>
+        <v>0.004883346019859347</v>
       </c>
       <c r="C17" t="n">
-        <v>0.009496249298068905</v>
+        <v>0.003036530678676753</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01531401686073256</v>
+        <v>0.007860941160250727</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02411597229216642</v>
+        <v>0.004329354175806414</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02496032621832666</v>
+        <v>0.00594895400863656</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.008335327858213693</v>
+        <v>0.07935437282271439</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008863166011530978</v>
+        <v>0.08684477741015513</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01001301102432514</v>
+        <v>0.08284222607341152</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01134869284337243</v>
+        <v>0.05700316331478446</v>
       </c>
       <c r="F18" t="n">
-        <v>0.004597954829691754</v>
+        <v>0.06676048387469917</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Nterm_mono</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.03750897536196161</v>
+        <v>0.009766692039718694</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02595641474805501</v>
+        <v>0.007894979764559556</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01767001945469142</v>
+        <v>0.01209375563115496</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01631374596234787</v>
+        <v>0.01443118058602138</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0223329234585028</v>
+        <v>0.00594895400863656</v>
       </c>
     </row>
     <row r="20">
@@ -858,85 +858,85 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1000239342985643</v>
+        <v>0.1092648671943529</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1399114063248819</v>
+        <v>0.1257123700972176</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06184506809141997</v>
+        <v>0.08284222607341152</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06099922403312683</v>
+        <v>0.06421875360779514</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03875419070740192</v>
+        <v>0.05486257585742604</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.01131223066471858</v>
+        <v>0.1507733083631574</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009496249298068905</v>
+        <v>0.1603288198341326</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01001301102432514</v>
+        <v>0.1560094476418991</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01773233256776943</v>
+        <v>0.115449444688171</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001970552069867894</v>
+        <v>0.1050981874859125</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01964755852293227</v>
+        <v>0.01953338407943739</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02215791502882745</v>
+        <v>0.01943379634353122</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01767001945469142</v>
+        <v>0.02297813569919444</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01489515935692632</v>
+        <v>0.008658708351612828</v>
       </c>
       <c r="F22" t="n">
-        <v>0.007882208279471578</v>
+        <v>0.01388089268681864</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Formylation</t>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.002381522245203912</v>
+        <v>0.02807923961419125</v>
       </c>
       <c r="C23" t="n">
-        <v>0.003798499719227562</v>
+        <v>0.01457534725764841</v>
       </c>
       <c r="D23" t="n">
-        <v>0.005301005836407427</v>
+        <v>0.01451250675738596</v>
       </c>
       <c r="E23" t="n">
-        <v>0.002127879908132331</v>
+        <v>0.01226650349811817</v>
       </c>
       <c r="F23" t="n">
-        <v>0.006568506899559648</v>
+        <v>0.004626964228939546</v>
       </c>
     </row>
     <row r="24">
@@ -946,173 +946,195 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02560136413594205</v>
+        <v>0.02624798485674399</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0303879977538205</v>
+        <v>0.02732877610809077</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02414902658807827</v>
+        <v>0.02418751126230993</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0184416258704802</v>
+        <v>0.01948209379112887</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0131370137991193</v>
+        <v>0.01189790801727312</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +26</t>
+          <t>Carboxyethyl</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00297690280650489</v>
+        <v>0.01037711029220111</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003798499719227562</v>
+        <v>0.009716898171765609</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002356002593958856</v>
+        <v>0.007860941160250727</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001418586605421554</v>
+        <v>0.01010182641021497</v>
       </c>
       <c r="F25" t="n">
-        <v>0.002627402759823859</v>
+        <v>0.002643979559394026</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Phosphorylation</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.03274593087155379</v>
+        <v>0.02075422058440222</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002532333146151708</v>
+        <v>0.01882649020779587</v>
       </c>
       <c r="D26" t="n">
-        <v>0.006479007133386855</v>
+        <v>0.03325782798567616</v>
       </c>
       <c r="E26" t="n">
-        <v>0.003546466513553885</v>
+        <v>0.01587429864462352</v>
       </c>
       <c r="F26" t="n">
-        <v>0.003284253449779824</v>
+        <v>0.02776178537363727</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.01845679740033032</v>
+        <v>0.0164812928170253</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01772633202306196</v>
+        <v>0.01396804112191306</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01413601556375314</v>
+        <v>0.01330313119427046</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005674346421686217</v>
+        <v>0.008658708351612828</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01248016310916333</v>
+        <v>0.008592933568030585</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02619674469724303</v>
+        <v>0.06775642602554845</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02215791502882745</v>
+        <v>0.04068951109426849</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03003903307297542</v>
+        <v>0.03809533023813814</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01134869284337243</v>
+        <v>0.00793714932231176</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02758772897815052</v>
+        <v>0.01850785691575818</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Persulfide</t>
+          <t>Acrylamide adduct</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.007144566735611736</v>
+        <v>0.07080851728796053</v>
       </c>
       <c r="C29" t="n">
-        <v>0.005697749578841343</v>
+        <v>0.07348404242397742</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008835009727345711</v>
+        <v>0.07981878716562277</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008511519632529324</v>
+        <v>0.07792837516451546</v>
       </c>
       <c r="F29" t="n">
-        <v>0.009852760349339473</v>
+        <v>0.05354058607772903</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Prompt loss of side chain from oxidised Met</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01250299178732054</v>
+        <v>0.01159794679716595</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0164601654499861</v>
+        <v>0.01336073498617771</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03003903307297542</v>
+        <v>0.01511719453894371</v>
       </c>
       <c r="E30" t="n">
-        <v>0.009220812935240102</v>
+        <v>0.02525456602553742</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01707811793885508</v>
+        <v>0.02643979559394026</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.02321984189073814</v>
+        <v>0.625678708794479</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01835941530959988</v>
+        <v>0.9334295306252338</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04240804669125942</v>
+        <v>0.7776284870832643</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0312089053192742</v>
+        <v>0.4379863307857489</v>
       </c>
       <c r="F31" t="n">
-        <v>0.02167607276854684</v>
+        <v>0.3628861945268301</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Oxidation to nitro</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.1153690497191771</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1305708191831004</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1880579000644597</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.1053476182779561</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0707264532137902</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Ping_2018/acg/PTM_heatmap_data.xlsx
+++ b/Dependencies/Ping_2018/acg/PTM_heatmap_data.xlsx
@@ -458,683 +458,683 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05188555146100556</v>
+        <v>0.002441673009929674</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07166212401677137</v>
+        <v>0.01032420430750096</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05563127590331284</v>
+        <v>0.01330313119427046</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04257198272876307</v>
+        <v>0.00793714932231176</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04494765250969844</v>
+        <v>0.005287959118788052</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Lys_mono</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006104182524824184</v>
+        <v>0.06775642602554845</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006073061357353506</v>
+        <v>0.04068951109426849</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01088438006803947</v>
+        <v>0.03809533023813814</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005772472234408552</v>
+        <v>0.00793714932231176</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00594895400863656</v>
+        <v>0.01850785691575818</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Persulfide</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007935437282271439</v>
+        <v>0.0134292015546132</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007894979764559556</v>
+        <v>0.01578995952911911</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008465628941808476</v>
+        <v>0.03446720354879165</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01010182641021497</v>
+        <v>0.0115449444688171</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0105759182375761</v>
+        <v>0.01189790801727312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +26</t>
+          <t>Persulfide</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02807923961419125</v>
+        <v>0.007935437282271439</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02489955156514937</v>
+        <v>0.007894979764559556</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02721095017009867</v>
+        <v>0.008465628941808476</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02020365282042993</v>
+        <v>0.01010182641021497</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02908377515333429</v>
+        <v>0.0105759182375761</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Phosphorylation</t>
+          <t>Formylation</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0366250951489451</v>
+        <v>0.004883346019859347</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002429224542941402</v>
+        <v>0.003036530678676753</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003628126689346489</v>
+        <v>0.007860941160250727</v>
       </c>
       <c r="E6" t="n">
         <v>0.004329354175806414</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003304974449242533</v>
+        <v>0.00594895400863656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01281878330213079</v>
+        <v>0.02807923961419125</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009109592036030258</v>
+        <v>0.02489955156514937</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01330313119427046</v>
+        <v>0.02721095017009867</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009380267380913897</v>
+        <v>0.02020365282042993</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002643979559394026</v>
+        <v>0.02908377515333429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01037711029220111</v>
+        <v>0.1507733083631574</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004858449085882804</v>
+        <v>0.1603288198341326</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01088438006803947</v>
+        <v>0.1560094476418991</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01731741670322566</v>
+        <v>0.115449444688171</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003304974449242533</v>
+        <v>0.1050981874859125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.534051877005605</v>
+        <v>0.01281878330213079</v>
       </c>
       <c r="C9" t="n">
-        <v>5.620618286230669</v>
+        <v>0.009109592036030258</v>
       </c>
       <c r="D9" t="n">
-        <v>5.700391716744893</v>
+        <v>0.01330313119427046</v>
       </c>
       <c r="E9" t="n">
-        <v>7.291353991087303</v>
+        <v>0.009380267380913897</v>
       </c>
       <c r="F9" t="n">
-        <v>5.262180318083961</v>
+        <v>0.002643979559394026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002441673009929674</v>
+        <v>0.01037711029220111</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01032420430750096</v>
+        <v>0.004858449085882804</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01330313119427046</v>
+        <v>0.01088438006803947</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00793714932231176</v>
+        <v>0.01731741670322566</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005287959118788052</v>
+        <v>0.003304974449242533</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Carbamylation</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0433396959262517</v>
+        <v>0.1153690497191771</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03826028655132709</v>
+        <v>0.1305708191831004</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02842032573321417</v>
+        <v>0.1880579000644597</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02597612505483849</v>
+        <v>0.1053476182779561</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02643979559394026</v>
+        <v>0.0707264532137902</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7953749829845912</v>
+        <v>0.02807923961419125</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9552925515117066</v>
+        <v>0.02732877610809077</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2884360718030459</v>
+        <v>0.0362812668934649</v>
       </c>
       <c r="E12" t="n">
-        <v>0.292952965896234</v>
+        <v>0.01587429864462352</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2313482114469773</v>
+        <v>0.03304974449242533</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Acetylation</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02807923961419125</v>
+        <v>0.006714600777306602</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02732877610809077</v>
+        <v>0.004251142950147454</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0362812668934649</v>
+        <v>0.003023438907788741</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01587429864462352</v>
+        <v>0.004329354175806414</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03304974449242533</v>
+        <v>0.00198298466954552</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0134292015546132</v>
+        <v>0.7953749829845912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01578995952911911</v>
+        <v>0.9552925515117066</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03446720354879165</v>
+        <v>0.2884360718030459</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0115449444688171</v>
+        <v>0.292952965896234</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01189790801727312</v>
+        <v>0.2313482114469773</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Acetylation</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.006714600777306602</v>
+        <v>5.534051877005605</v>
       </c>
       <c r="C15" t="n">
-        <v>0.004251142950147454</v>
+        <v>5.620618286230669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003023438907788741</v>
+        <v>5.700391716744893</v>
       </c>
       <c r="E15" t="n">
-        <v>0.004329354175806414</v>
+        <v>7.291353991087303</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00198298466954552</v>
+        <v>5.262180318083961</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Prompt loss of side chain from oxidised Met</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1660337646752178</v>
+        <v>0.01159794679716595</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1469680848479548</v>
+        <v>0.01336073498617771</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1027969228648172</v>
+        <v>0.01511719453894371</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03391327437715025</v>
+        <v>0.02525456602553742</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02776178537363727</v>
+        <v>0.02643979559394026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Formylation</t>
+          <t>Quinone</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.004883346019859347</v>
+        <v>0.02624798485674399</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003036530678676753</v>
+        <v>0.02732877610809077</v>
       </c>
       <c r="D17" t="n">
-        <v>0.007860941160250727</v>
+        <v>0.02418751126230993</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004329354175806414</v>
+        <v>0.01948209379112887</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00594895400863656</v>
+        <v>0.01189790801727312</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Missing TMT10_Lys_mono</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.07935437282271439</v>
+        <v>0.006104182524824184</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08684477741015513</v>
+        <v>0.006073061357353506</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08284222607341152</v>
+        <v>0.01088438006803947</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05700316331478446</v>
+        <v>0.005772472234408552</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06676048387469917</v>
+        <v>0.00594895400863656</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Carbamylation</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.009766692039718694</v>
+        <v>0.0433396959262517</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007894979764559556</v>
+        <v>0.03826028655132709</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01209375563115496</v>
+        <v>0.02842032573321417</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01443118058602138</v>
+        <v>0.02597612505483849</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00594895400863656</v>
+        <v>0.02643979559394026</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1092648671943529</v>
+        <v>0.07935437282271439</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1257123700972176</v>
+        <v>0.08684477741015513</v>
       </c>
       <c r="D20" t="n">
         <v>0.08284222607341152</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06421875360779514</v>
+        <v>0.05700316331478446</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05486257585742604</v>
+        <v>0.06676048387469917</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1507733083631574</v>
+        <v>0.1660337646752178</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1603288198341326</v>
+        <v>0.1469680848479548</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1560094476418991</v>
+        <v>0.1027969228648172</v>
       </c>
       <c r="E21" t="n">
-        <v>0.115449444688171</v>
+        <v>0.03391327437715025</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1050981874859125</v>
+        <v>0.02776178537363727</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Acrylamide adduct</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01953338407943739</v>
+        <v>0.07080851728796053</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01943379634353122</v>
+        <v>0.07348404242397742</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02297813569919444</v>
+        <v>0.07981878716562277</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008658708351612828</v>
+        <v>0.07792837516451546</v>
       </c>
       <c r="F22" t="n">
-        <v>0.01388089268681864</v>
+        <v>0.05354058607772903</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
+          <t>Carboxyethyl</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02807923961419125</v>
+        <v>0.01037711029220111</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01457534725764841</v>
+        <v>0.009716898171765609</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01451250675738596</v>
+        <v>0.007860941160250727</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01226650349811817</v>
+        <v>0.01010182641021497</v>
       </c>
       <c r="F23" t="n">
-        <v>0.004626964228939546</v>
+        <v>0.002643979559394026</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Quinone</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02624798485674399</v>
+        <v>0.05188555146100556</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02732877610809077</v>
+        <v>0.07166212401677137</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02418751126230993</v>
+        <v>0.05563127590331284</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01948209379112887</v>
+        <v>0.04257198272876307</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01189790801727312</v>
+        <v>0.04494765250969844</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Carboxyethyl</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01037711029220111</v>
+        <v>0.01953338407943739</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009716898171765609</v>
+        <v>0.01943379634353122</v>
       </c>
       <c r="D25" t="n">
-        <v>0.007860941160250727</v>
+        <v>0.02297813569919444</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01010182641021497</v>
+        <v>0.008658708351612828</v>
       </c>
       <c r="F25" t="n">
-        <v>0.002643979559394026</v>
+        <v>0.01388089268681864</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Phosphorylation</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02075422058440222</v>
+        <v>0.0366250951489451</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01882649020779587</v>
+        <v>0.002429224542941402</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03325782798567616</v>
+        <v>0.003628126689346489</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01587429864462352</v>
+        <v>0.004329354175806414</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02776178537363727</v>
+        <v>0.003304974449242533</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0164812928170253</v>
+        <v>0.009766692039718694</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01396804112191306</v>
+        <v>0.007894979764559556</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01330313119427046</v>
+        <v>0.01209375563115496</v>
       </c>
       <c r="E27" t="n">
-        <v>0.008658708351612828</v>
+        <v>0.01443118058602138</v>
       </c>
       <c r="F27" t="n">
-        <v>0.008592933568030585</v>
+        <v>0.00594895400863656</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.06775642602554845</v>
+        <v>0.625678708794479</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04068951109426849</v>
+        <v>0.9334295306252338</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03809533023813814</v>
+        <v>0.7776284870832643</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00793714932231176</v>
+        <v>0.4379863307857489</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01850785691575818</v>
+        <v>0.3628861945268301</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Acrylamide adduct</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.07080851728796053</v>
+        <v>0.02075422058440222</v>
       </c>
       <c r="C29" t="n">
-        <v>0.07348404242397742</v>
+        <v>0.01882649020779587</v>
       </c>
       <c r="D29" t="n">
-        <v>0.07981878716562277</v>
+        <v>0.03325782798567616</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07792837516451546</v>
+        <v>0.01587429864462352</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05354058607772903</v>
+        <v>0.02776178537363727</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01159794679716595</v>
+        <v>0.0164812928170253</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01336073498617771</v>
+        <v>0.01396804112191306</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01511719453894371</v>
+        <v>0.01330313119427046</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02525456602553742</v>
+        <v>0.008658708351612828</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02643979559394026</v>
+        <v>0.008592933568030585</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.625678708794479</v>
+        <v>0.02807923961419125</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9334295306252338</v>
+        <v>0.01457534725764841</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7776284870832643</v>
+        <v>0.01451250675738596</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4379863307857489</v>
+        <v>0.01226650349811817</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3628861945268301</v>
+        <v>0.004626964228939546</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1153690497191771</v>
+        <v>0.1092648671943529</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1305708191831004</v>
+        <v>0.1257123700972176</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1880579000644597</v>
+        <v>0.08284222607341152</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1053476182779561</v>
+        <v>0.06421875360779514</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0707264532137902</v>
+        <v>0.05486257585742604</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Ping_2018/acg/PTM_heatmap_data.xlsx
+++ b/Dependencies/Ping_2018/acg/PTM_heatmap_data.xlsx
@@ -458,683 +458,683 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Iodoacetamide derivative</t>
+          <t>Acetaldehyde +26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002441673009929674</v>
+        <v>0.02204998732125729</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01032420430750096</v>
+        <v>0.01948312689930787</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01330313119427046</v>
+        <v>0.02074036656062962</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00793714932231176</v>
+        <v>0.01368116723809971</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005287959118788052</v>
+        <v>0.02145894489294181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Replacement of proton with ammonium ion</t>
+          <t>Carbamylation</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06775642602554845</v>
+        <v>0.03403367608281016</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04068951109426849</v>
+        <v>0.02993748767454624</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03809533023813814</v>
+        <v>0.02166216062999094</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00793714932231176</v>
+        <v>0.01759007216327105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01850785691575818</v>
+        <v>0.01950813172085619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Cysteine oxidation to cysteic acid</t>
+          <t>Reduction</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0134292015546132</v>
+        <v>0.01629781671571191</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01578995952911911</v>
+        <v>0.01473114472874498</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03446720354879165</v>
+        <v>0.0253493369074362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0115449444688171</v>
+        <v>0.0107494885442212</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01189790801727312</v>
+        <v>0.020483538306899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Persulfide</t>
+          <t>2-amino-3-oxo-butanoic_acid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007935437282271439</v>
+        <v>0.06231518156007495</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007894979764559556</v>
+        <v>0.06795334503904941</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008465628941808476</v>
+        <v>0.06314289375125018</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01010182641021497</v>
+        <v>0.03860043613606703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0105759182375761</v>
+        <v>0.04925803259516189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Formylation</t>
+          <t>Sodium adduct</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004883346019859347</v>
+        <v>0.1303825337256953</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003036530678676753</v>
+        <v>0.1149979685276221</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007860941160250727</v>
+        <v>0.0783524958957119</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004329354175806414</v>
+        <v>0.02296481643538165</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00594895400863656</v>
+        <v>0.020483538306899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Acetaldehyde +26</t>
+          <t>Replacement of proton with ammonium ion</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02807923961419125</v>
+        <v>0.05320757810129476</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02489955156514937</v>
+        <v>0.0318382805427714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02721095017009867</v>
+        <v>0.02903651318488147</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02020365282042993</v>
+        <v>0.005374744272110599</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02908377515333429</v>
+        <v>0.01365569220459934</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DTT adduct of cysteine</t>
+          <t>Carboxyethyl</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1507733083631574</v>
+        <v>0.008148908357855955</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1603288198341326</v>
+        <v>0.007603171472900633</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1560094476418991</v>
+        <v>0.005991661450848557</v>
       </c>
       <c r="E8" t="n">
-        <v>0.115449444688171</v>
+        <v>0.006840583619049853</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1050981874859125</v>
+        <v>0.001950813172085619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Deamidation followed by a methylation</t>
+          <t>Deamidation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01281878330213079</v>
+        <v>0.6245898582521359</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009109592036030258</v>
+        <v>0.7474867954295435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01330313119427046</v>
+        <v>0.219847885542674</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009380267380913897</v>
+        <v>0.1983769249524457</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002643979559394026</v>
+        <v>0.1706961525574917</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Half of a disulfide bridge</t>
+          <t>Cysteine oxidation to cysteic acid</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01037711029220111</v>
+        <v>0.01054564611016653</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004858449085882804</v>
+        <v>0.01235515364346353</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01088438006803947</v>
+        <v>0.02627113097679752</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01731741670322566</v>
+        <v>0.007817809850342689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003304974449242533</v>
+        <v>0.008778659274385286</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Oxidation to nitro</t>
+          <t>Dihydroxy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1153690497191771</v>
+        <v>0.4913312392236679</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1305708191831004</v>
+        <v>0.730379659615517</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1880579000644597</v>
+        <v>0.5927135865993265</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1053476182779561</v>
+        <v>0.2965881611973757</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0707264532137902</v>
+        <v>0.2677491078687512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Conversion of carboxylic acid to hydroxamic acid</t>
+          <t>Missing TMT10_Lys_mono</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02807923961419125</v>
+        <v>0.00479347550462115</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02732877610809077</v>
+        <v>0.004751982170562895</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0362812668934649</v>
+        <v>0.008296146624251849</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01587429864462352</v>
+        <v>0.003908904925171344</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03304974449242533</v>
+        <v>0.004389329637192643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Acetylation</t>
+          <t>Conversion of carboxylic acid to hydroxamic acid</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.006714600777306602</v>
+        <v>0.02204998732125729</v>
       </c>
       <c r="C13" t="n">
-        <v>0.004251142950147454</v>
+        <v>0.02138391976753303</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003023438907788741</v>
+        <v>0.0276538220808395</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004329354175806414</v>
+        <v>0.0107494885442212</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00198298466954552</v>
+        <v>0.02438516465107024</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Deamidation</t>
+          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7953749829845912</v>
+        <v>0.02204998732125729</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9552925515117066</v>
+        <v>0.01140475720935095</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2884360718030459</v>
+        <v>0.0110615288323358</v>
       </c>
       <c r="E14" t="n">
-        <v>0.292952965896234</v>
+        <v>0.008306422965989105</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2313482114469773</v>
+        <v>0.003413923051149834</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Oxidation or Hydroxylation</t>
+          <t>Phosphorylation</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.534051877005605</v>
+        <v>0.0287608530277269</v>
       </c>
       <c r="C15" t="n">
-        <v>5.620618286230669</v>
+        <v>0.001900792868225158</v>
       </c>
       <c r="D15" t="n">
-        <v>5.700391716744893</v>
+        <v>0.00276538220808395</v>
       </c>
       <c r="E15" t="n">
-        <v>7.291353991087303</v>
+        <v>0.002931678693878508</v>
       </c>
       <c r="F15" t="n">
-        <v>5.262180318083961</v>
+        <v>0.002438516465107024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Prompt loss of side chain from oxidised Met</t>
+          <t>Formylation</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01159794679716595</v>
+        <v>0.00383478040369692</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01336073498617771</v>
+        <v>0.002375991085281448</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01511719453894371</v>
+        <v>0.005991661450848557</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02525456602553742</v>
+        <v>0.002931678693878508</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02643979559394026</v>
+        <v>0.004389329637192643</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Quinone</t>
+          <t>Prompt loss of side chain from oxidised Met</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02624798485674399</v>
+        <v>0.009107603458780185</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02732877610809077</v>
+        <v>0.01045436077523837</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02418751126230993</v>
+        <v>0.01152242586701646</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01948209379112887</v>
+        <v>0.01710145904762463</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01189790801727312</v>
+        <v>0.01950813172085619</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Missing TMT10_Lys_mono</t>
+          <t>Quinone</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.006104182524824184</v>
+        <v>0.02061194466987095</v>
       </c>
       <c r="C18" t="n">
-        <v>0.006073061357353506</v>
+        <v>0.02138391976753303</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01088438006803947</v>
+        <v>0.01843588138722633</v>
       </c>
       <c r="E18" t="n">
-        <v>0.005772472234408552</v>
+        <v>0.01319255412245329</v>
       </c>
       <c r="F18" t="n">
-        <v>0.00594895400863656</v>
+        <v>0.008778659274385286</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Carbamylation</t>
+          <t>Deamidation followed by a methylation</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0433396959262517</v>
+        <v>0.01006629855970441</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03826028655132709</v>
+        <v>0.007127973255844344</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02842032573321417</v>
+        <v>0.01013973476297448</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02597612505483849</v>
+        <v>0.006351970503403434</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02643979559394026</v>
+        <v>0.001950813172085619</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2-amino-3-oxo-butanoic_acid</t>
+          <t>Dehydration</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07935437282271439</v>
+        <v>0.08580321153271858</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08684477741015513</v>
+        <v>0.09836603093065194</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08284222607341152</v>
+        <v>0.06314289375125018</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05700316331478446</v>
+        <v>0.0434865672925312</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06676048387469917</v>
+        <v>0.0404793733207766</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Sodium adduct</t>
+          <t>Replacement of 2 protons by magnesium</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1660337646752178</v>
+        <v>0.01294238386247711</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1469680848479548</v>
+        <v>0.01092955899229466</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1027969228648172</v>
+        <v>0.01013973476297448</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03391327437715025</v>
+        <v>0.005863357387757016</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02776178537363727</v>
+        <v>0.006340142809278262</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Acrylamide adduct</t>
+          <t>Half of a disulfide bridge</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07080851728796053</v>
+        <v>0.008148908357855955</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07348404242397742</v>
+        <v>0.003801585736450317</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07981878716562277</v>
+        <v>0.008296146624251849</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07792837516451546</v>
+        <v>0.01172671477551403</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05354058607772903</v>
+        <v>0.002438516465107024</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Carboxyethyl</t>
+          <t>Acrylamide adduct</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01037711029220111</v>
+        <v>0.05560431585360534</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009716898171765609</v>
+        <v>0.05749898426381105</v>
       </c>
       <c r="D23" t="n">
-        <v>0.007860941160250727</v>
+        <v>0.06083840857784688</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01010182641021497</v>
+        <v>0.05277021648981315</v>
       </c>
       <c r="F23" t="n">
-        <v>0.002643979559394026</v>
+        <v>0.03950396673473379</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Methylation</t>
+          <t>DTT adduct of cysteine</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.05188555146100556</v>
+        <v>0.1183988449641424</v>
       </c>
       <c r="C24" t="n">
-        <v>0.07166212401677137</v>
+        <v>0.1254523293028604</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05563127590331284</v>
+        <v>0.1189114349476098</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04257198272876307</v>
+        <v>0.07817809850342688</v>
       </c>
       <c r="F24" t="n">
-        <v>0.04494765250969844</v>
+        <v>0.07754482359040336</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Loss of ammonia</t>
+          <t>Amidation</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01953338407943739</v>
+        <v>0.00766956080739384</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01943379634353122</v>
+        <v>0.006177576821731764</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02297813569919444</v>
+        <v>0.009217940693613164</v>
       </c>
       <c r="E25" t="n">
-        <v>0.008658708351612828</v>
+        <v>0.009772262312928361</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01388089268681864</v>
+        <v>0.004389329637192643</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Phosphorylation</t>
+          <t>Acetylation</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0366250951489451</v>
+        <v>0.005272823055083265</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002429224542941402</v>
+        <v>0.003326387519394027</v>
       </c>
       <c r="D26" t="n">
-        <v>0.003628126689346489</v>
+        <v>0.002304485173403291</v>
       </c>
       <c r="E26" t="n">
-        <v>0.004329354175806414</v>
+        <v>0.002931678693878508</v>
       </c>
       <c r="F26" t="n">
-        <v>0.003304974449242533</v>
+        <v>0.001463109879064214</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Amidation</t>
+          <t>Loss of ammonia</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.009766692039718694</v>
+        <v>0.01533912161478768</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007894979764559556</v>
+        <v>0.01520634294580127</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01209375563115496</v>
+        <v>0.01751408731786501</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01443118058602138</v>
+        <v>0.005863357387757016</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00594895400863656</v>
+        <v>0.0102417691534495</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Dihydroxy</t>
+          <t>Methylation</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.625678708794479</v>
+        <v>0.04074454178927978</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9334295306252338</v>
+        <v>0.05607338961264217</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7776284870832643</v>
+        <v>0.04240252719062056</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4379863307857489</v>
+        <v>0.02882817382313866</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3628861945268301</v>
+        <v>0.03316382392545553</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Reduction</t>
+          <t>Iodoacetamide derivative</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02075422058440222</v>
+        <v>0.00191739020184846</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01882649020779587</v>
+        <v>0.008078369689956922</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03325782798567616</v>
+        <v>0.01013973476297448</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01587429864462352</v>
+        <v>0.005374744272110599</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02776178537363727</v>
+        <v>0.003901626344171238</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Replacement of 2 protons by magnesium</t>
+          <t>Oxidation or Hydroxylation</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0164812928170253</v>
+        <v>4.345764892489535</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01396804112191306</v>
+        <v>4.39795949885596</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01330313119427046</v>
+        <v>4.344876345934566</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008658708351612828</v>
+        <v>4.937435533607054</v>
       </c>
       <c r="F30" t="n">
-        <v>0.008592933568030585</v>
+        <v>3.882605915743404</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Succinic anhydride labeling reagent light form (N-term &amp; K)</t>
+          <t>Oxidation to nitro</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.02807923961419125</v>
+        <v>0.09059668703733974</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01457534725764841</v>
+        <v>0.1021676166671023</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01451250675738596</v>
+        <v>0.1433389777856847</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01226650349811817</v>
+        <v>0.07133751488437703</v>
       </c>
       <c r="F31" t="n">
-        <v>0.004626964228939546</v>
+        <v>0.05218425235329031</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Dehydration</t>
+          <t>Persulfide</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1092648671943529</v>
+        <v>0.006231518156007494</v>
       </c>
       <c r="C32" t="n">
-        <v>0.1257123700972176</v>
+        <v>0.006177576821731764</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08284222607341152</v>
+        <v>0.006452558485529216</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06421875360779514</v>
+        <v>0.006840583619049853</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05486257585742604</v>
+        <v>0.007803252688342477</v>
       </c>
     </row>
   </sheetData>
